--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/29.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/29.xlsx
@@ -426,13 +426,13 @@
         <v>-10.68977734903131</v>
       </c>
       <c r="E2">
-        <v>-7.634642447245203</v>
+        <v>-4.937990517365598</v>
       </c>
       <c r="F2">
-        <v>-6.054887893720479</v>
+        <v>-7.05270281896704</v>
       </c>
       <c r="G2">
-        <v>-6.037363597544255</v>
+        <v>-7.292778745310057</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.51570348043211</v>
       </c>
       <c r="E3">
-        <v>-7.275353319476637</v>
+        <v>-5.028741136479312</v>
       </c>
       <c r="F3">
-        <v>-6.332834150218811</v>
+        <v>-6.737841197530351</v>
       </c>
       <c r="G3">
-        <v>-5.83666177422594</v>
+        <v>-7.060481075364937</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.65675537907517</v>
       </c>
       <c r="E4">
-        <v>-8.008612887746636</v>
+        <v>-5.98060825899559</v>
       </c>
       <c r="F4">
-        <v>-6.389367326173967</v>
+        <v>-6.79373031782983</v>
       </c>
       <c r="G4">
-        <v>-6.029871832988885</v>
+        <v>-7.414778969523279</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.93718270833423</v>
       </c>
       <c r="E5">
-        <v>-9.097402950358836</v>
+        <v>-6.892801420730668</v>
       </c>
       <c r="F5">
-        <v>-5.871758226881384</v>
+        <v>-6.391148730273687</v>
       </c>
       <c r="G5">
-        <v>-5.849963546202731</v>
+        <v>-7.271713744043675</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.29841673195324</v>
       </c>
       <c r="E6">
-        <v>-8.45825865739025</v>
+        <v>-7.67716028970322</v>
       </c>
       <c r="F6">
-        <v>-6.097953058257219</v>
+        <v>-6.700781696663906</v>
       </c>
       <c r="G6">
-        <v>-6.648741905554701</v>
+        <v>-8.021976058517625</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.62101531190942</v>
       </c>
       <c r="E7">
-        <v>-9.924999689156625</v>
+        <v>-7.984516877551822</v>
       </c>
       <c r="F7">
-        <v>-6.273689546026329</v>
+        <v>-6.458134246117368</v>
       </c>
       <c r="G7">
-        <v>-5.791668149801705</v>
+        <v>-7.673011453223049</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.80495980011385</v>
       </c>
       <c r="E8">
-        <v>-10.89645699023009</v>
+        <v>-8.439275294350095</v>
       </c>
       <c r="F8">
-        <v>-6.281038407440264</v>
+        <v>-6.58454518270308</v>
       </c>
       <c r="G8">
-        <v>-6.940602910842388</v>
+        <v>-7.395269924660353</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.73254881049743</v>
       </c>
       <c r="E9">
-        <v>-11.44544389417996</v>
+        <v>-10.23593829994529</v>
       </c>
       <c r="F9">
-        <v>-6.104990867711404</v>
+        <v>-6.327999798056073</v>
       </c>
       <c r="G9">
-        <v>-5.672852670397262</v>
+        <v>-7.390314037988064</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.31261632223818</v>
       </c>
       <c r="E10">
-        <v>-11.81347750525734</v>
+        <v>-9.838243184117676</v>
       </c>
       <c r="F10">
-        <v>-6.080537461980763</v>
+        <v>-6.265764140900044</v>
       </c>
       <c r="G10">
-        <v>-6.332955587654701</v>
+        <v>-6.789221594968135</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.46992690943778</v>
       </c>
       <c r="E11">
-        <v>-12.5970710621226</v>
+        <v>-10.99059037942753</v>
       </c>
       <c r="F11">
-        <v>-5.446289676353293</v>
+        <v>-6.071537250149346</v>
       </c>
       <c r="G11">
-        <v>-5.907454480037715</v>
+        <v>-7.416169398649773</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.16381565577202</v>
       </c>
       <c r="E12">
-        <v>-12.41173873488468</v>
+        <v>-10.46771465660588</v>
       </c>
       <c r="F12">
-        <v>-5.681368748124154</v>
+        <v>-6.127138098592652</v>
       </c>
       <c r="G12">
-        <v>-5.148518536250873</v>
+        <v>-6.70748091505799</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.38360905362295</v>
       </c>
       <c r="E13">
-        <v>-12.63558120508382</v>
+        <v>-11.37055199104111</v>
       </c>
       <c r="F13">
-        <v>-5.886846110755974</v>
+        <v>-5.841640444850399</v>
       </c>
       <c r="G13">
-        <v>-5.074574191085712</v>
+        <v>-6.405900148067002</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.16348572326746</v>
       </c>
       <c r="E14">
-        <v>-14.69846414064195</v>
+        <v>-12.29206022380997</v>
       </c>
       <c r="F14">
-        <v>-5.000111112387812</v>
+        <v>-5.732444225445965</v>
       </c>
       <c r="G14">
-        <v>-5.412077687723332</v>
+        <v>-6.296357506718058</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.57505251455371</v>
       </c>
       <c r="E15">
-        <v>-14.51585795475665</v>
+        <v>-12.28438898884097</v>
       </c>
       <c r="F15">
-        <v>-4.979765580607653</v>
+        <v>-5.595096768224793</v>
       </c>
       <c r="G15">
-        <v>-4.443835812761608</v>
+        <v>-5.840607944508751</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.72661521118119</v>
       </c>
       <c r="E16">
-        <v>-15.57230112753206</v>
+        <v>-13.47032840433972</v>
       </c>
       <c r="F16">
-        <v>-5.185457490396798</v>
+        <v>-5.471396663964743</v>
       </c>
       <c r="G16">
-        <v>-3.840995401696943</v>
+        <v>-5.490915019195535</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-11.75410790564133</v>
       </c>
       <c r="E17">
-        <v>-16.36205793752175</v>
+        <v>-13.49448328469664</v>
       </c>
       <c r="F17">
-        <v>-4.711985048876477</v>
+        <v>-5.381776423023267</v>
       </c>
       <c r="G17">
-        <v>-2.840426049544237</v>
+        <v>-4.669942762548291</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.80550234456612</v>
       </c>
       <c r="E18">
-        <v>-15.7108316759007</v>
+        <v>-15.10474977166212</v>
       </c>
       <c r="F18">
-        <v>-4.246008503984088</v>
+        <v>-4.867058740150155</v>
       </c>
       <c r="G18">
-        <v>-3.107994271664753</v>
+        <v>-4.249473684150997</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.021664849991208</v>
       </c>
       <c r="E19">
-        <v>-18.1760468846703</v>
+        <v>-15.09961448213742</v>
       </c>
       <c r="F19">
-        <v>-4.320712333103352</v>
+        <v>-4.691998200181731</v>
       </c>
       <c r="G19">
-        <v>-2.50877559742005</v>
+        <v>-4.375900107750224</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.51723236682964</v>
       </c>
       <c r="E20">
-        <v>-18.68037850643054</v>
+        <v>-15.18701403048546</v>
       </c>
       <c r="F20">
-        <v>-3.967945447681961</v>
+        <v>-4.648387141526545</v>
       </c>
       <c r="G20">
-        <v>-2.408581936674008</v>
+        <v>-4.525261990845522</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.376372097083729</v>
       </c>
       <c r="E21">
-        <v>-19.09263719466682</v>
+        <v>-15.79372992108512</v>
       </c>
       <c r="F21">
-        <v>-3.503829415976259</v>
+        <v>-4.325327167904349</v>
       </c>
       <c r="G21">
-        <v>-2.755139775361533</v>
+        <v>-3.955858089727496</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.638306888054319</v>
       </c>
       <c r="E22">
-        <v>-19.54777600328174</v>
+        <v>-15.65429367791494</v>
       </c>
       <c r="F22">
-        <v>-3.418500946548688</v>
+        <v>-4.186537523034903</v>
       </c>
       <c r="G22">
-        <v>-3.122001189841409</v>
+        <v>-4.340179321381489</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.301551807785724</v>
       </c>
       <c r="E23">
-        <v>-19.72028369212994</v>
+        <v>-16.40719776643021</v>
       </c>
       <c r="F23">
-        <v>-3.456549518094075</v>
+        <v>-4.263246829636345</v>
       </c>
       <c r="G23">
-        <v>-3.269548893981187</v>
+        <v>-4.15788744180706</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.329480349555581</v>
       </c>
       <c r="E24">
-        <v>-20.05160949290114</v>
+        <v>-17.36761917634698</v>
       </c>
       <c r="F24">
-        <v>-2.862786532543625</v>
+        <v>-3.629245069127507</v>
       </c>
       <c r="G24">
-        <v>-3.321597290949608</v>
+        <v>-3.622979425208239</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.658263604841492</v>
       </c>
       <c r="E25">
-        <v>-20.495499572081</v>
+        <v>-17.72491124707816</v>
       </c>
       <c r="F25">
-        <v>-3.142832700408055</v>
+        <v>-3.542547308383108</v>
       </c>
       <c r="G25">
-        <v>-3.233559953423769</v>
+        <v>-4.318472074280487</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.206697978277815</v>
       </c>
       <c r="E26">
-        <v>-21.72160655202779</v>
+        <v>-17.64964348059667</v>
       </c>
       <c r="F26">
-        <v>-2.410012507317055</v>
+        <v>-3.768727229145694</v>
       </c>
       <c r="G26">
-        <v>-3.691752698241059</v>
+        <v>-4.133247051358264</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.892001892396562</v>
       </c>
       <c r="E27">
-        <v>-20.00082718537912</v>
+        <v>-17.93337954802127</v>
       </c>
       <c r="F27">
-        <v>-3.105058318472994</v>
+        <v>-3.718916668847957</v>
       </c>
       <c r="G27">
-        <v>-4.156083194488157</v>
+        <v>-4.248609631765247</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.640163983246606</v>
       </c>
       <c r="E28">
-        <v>-20.99942363118055</v>
+        <v>-18.35762057848185</v>
       </c>
       <c r="F28">
-        <v>-2.949398971445536</v>
+        <v>-3.61581806189553</v>
       </c>
       <c r="G28">
-        <v>-4.710109611576269</v>
+        <v>-4.771162692411508</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.386400815211203</v>
       </c>
       <c r="E29">
-        <v>-21.33703948234841</v>
+        <v>-17.44824865605355</v>
       </c>
       <c r="F29">
-        <v>-2.968379353745882</v>
+        <v>-3.553261412370917</v>
       </c>
       <c r="G29">
-        <v>-3.720686866254289</v>
+        <v>-4.31423457599022</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.079532053390029</v>
       </c>
       <c r="E30">
-        <v>-21.45556776102517</v>
+        <v>-17.35483982269733</v>
       </c>
       <c r="F30">
-        <v>-2.821877608356372</v>
+        <v>-3.714090600359247</v>
       </c>
       <c r="G30">
-        <v>-3.843130703569773</v>
+        <v>-4.667920019223796</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.682437476185401</v>
       </c>
       <c r="E31">
-        <v>-20.55141264065371</v>
+        <v>-18.11152065853501</v>
       </c>
       <c r="F31">
-        <v>-3.023515488076217</v>
+        <v>-4.016447187483275</v>
       </c>
       <c r="G31">
-        <v>-4.426548143955534</v>
+        <v>-4.471922481116786</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.171945674068708</v>
       </c>
       <c r="E32">
-        <v>-20.87331921548896</v>
+        <v>-17.58689241627239</v>
       </c>
       <c r="F32">
-        <v>-3.494375258808109</v>
+        <v>-4.039562779858395</v>
       </c>
       <c r="G32">
-        <v>-4.005936712100052</v>
+        <v>-4.10196901710323</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.536670792456542</v>
       </c>
       <c r="E33">
-        <v>-20.09217103458784</v>
+        <v>-17.55174692949886</v>
       </c>
       <c r="F33">
-        <v>-3.281842691006645</v>
+        <v>-3.948219534719096</v>
       </c>
       <c r="G33">
-        <v>-2.825949033901005</v>
+        <v>-4.163104861576951</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.778027922649528</v>
       </c>
       <c r="E34">
-        <v>-20.14001889095289</v>
+        <v>-17.08615187440023</v>
       </c>
       <c r="F34">
-        <v>-3.453028956632177</v>
+        <v>-4.052049590088195</v>
       </c>
       <c r="G34">
-        <v>-3.307782384414229</v>
+        <v>-3.578568456798916</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.904010332259077</v>
       </c>
       <c r="E35">
-        <v>-19.3961355226609</v>
+        <v>-16.70337355195388</v>
       </c>
       <c r="F35">
-        <v>-3.374310030711543</v>
+        <v>-3.775566230423206</v>
       </c>
       <c r="G35">
-        <v>-3.540179370725528</v>
+        <v>-3.832619721482587</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.924632497619607</v>
       </c>
       <c r="E36">
-        <v>-18.86224202257858</v>
+        <v>-16.80245656324171</v>
       </c>
       <c r="F36">
-        <v>-3.048134567287418</v>
+        <v>-4.195010893198138</v>
       </c>
       <c r="G36">
-        <v>-2.638906521477722</v>
+        <v>-3.345969527209723</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.850525534416851</v>
       </c>
       <c r="E37">
-        <v>-19.18363687985096</v>
+        <v>-16.36683547759985</v>
       </c>
       <c r="F37">
-        <v>-3.435562001576747</v>
+        <v>-4.17576294822669</v>
       </c>
       <c r="G37">
-        <v>-3.244239773333458</v>
+        <v>-3.150508297480073</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.690930926893122</v>
       </c>
       <c r="E38">
-        <v>-19.08520596882024</v>
+        <v>-15.60347967107487</v>
       </c>
       <c r="F38">
-        <v>-3.26091233184011</v>
+        <v>-4.259995487580357</v>
       </c>
       <c r="G38">
-        <v>-2.660752811491372</v>
+        <v>-3.28152644774227</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.453516820807481</v>
       </c>
       <c r="E39">
-        <v>-19.33974696431738</v>
+        <v>-14.86636184295033</v>
       </c>
       <c r="F39">
-        <v>-3.320927550172934</v>
+        <v>-3.895469098508824</v>
       </c>
       <c r="G39">
-        <v>-3.352540960105176</v>
+        <v>-2.996660625179063</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.143357614132064</v>
       </c>
       <c r="E40">
-        <v>-18.79124007861232</v>
+        <v>-15.36226144610829</v>
       </c>
       <c r="F40">
-        <v>-3.211536664428843</v>
+        <v>-4.182785018700221</v>
       </c>
       <c r="G40">
-        <v>-1.543645635265242</v>
+        <v>-2.989235071534477</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.767816303864292</v>
       </c>
       <c r="E41">
-        <v>-18.99141221517337</v>
+        <v>-15.52794925310094</v>
       </c>
       <c r="F41">
-        <v>-3.587344589159103</v>
+        <v>-3.868061734619799</v>
       </c>
       <c r="G41">
-        <v>-1.282460144944442</v>
+        <v>-2.832470808613369</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.331875948158663</v>
       </c>
       <c r="E42">
-        <v>-17.43831318408072</v>
+        <v>-13.7384095371198</v>
       </c>
       <c r="F42">
-        <v>-3.207182765359728</v>
+        <v>-4.21597273032598</v>
       </c>
       <c r="G42">
-        <v>-1.823168237328066</v>
+        <v>-2.847014035167387</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.841214554210942</v>
       </c>
       <c r="E43">
-        <v>-17.39066005209801</v>
+        <v>-14.57754029921513</v>
       </c>
       <c r="F43">
-        <v>-3.086729032951249</v>
+        <v>-4.33707176094124</v>
       </c>
       <c r="G43">
-        <v>-1.751511479130541</v>
+        <v>-2.938126869499209</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.304236385048752</v>
       </c>
       <c r="E44">
-        <v>-17.31762029482829</v>
+        <v>-13.62677359588271</v>
       </c>
       <c r="F44">
-        <v>-3.507351634172963</v>
+        <v>-4.380400346312071</v>
       </c>
       <c r="G44">
-        <v>-1.220241752079379</v>
+        <v>-2.297208563641846</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.733561178385883</v>
       </c>
       <c r="E45">
-        <v>-16.67633856212808</v>
+        <v>-13.73063867572264</v>
       </c>
       <c r="F45">
-        <v>-3.269652436307048</v>
+        <v>-4.389755927759289</v>
       </c>
       <c r="G45">
-        <v>-2.363081798782264</v>
+        <v>-2.434818010072731</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.14681917125194</v>
       </c>
       <c r="E46">
-        <v>-15.78516657673661</v>
+        <v>-13.50163374515475</v>
       </c>
       <c r="F46">
-        <v>-3.702848826335855</v>
+        <v>-4.636697220738238</v>
       </c>
       <c r="G46">
-        <v>-1.635705285621295</v>
+        <v>-2.079437567523048</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.567497967671742</v>
       </c>
       <c r="E47">
-        <v>-16.66196971410175</v>
+        <v>-13.28529495638631</v>
       </c>
       <c r="F47">
-        <v>-3.476400514534762</v>
+        <v>-4.498695353268855</v>
       </c>
       <c r="G47">
-        <v>-1.568507832265169</v>
+        <v>-2.78686142271883</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.027738651365078</v>
       </c>
       <c r="E48">
-        <v>-15.87502961494482</v>
+        <v>-13.11506508996398</v>
       </c>
       <c r="F48">
-        <v>-3.528556182949825</v>
+        <v>-4.481680686815353</v>
       </c>
       <c r="G48">
-        <v>-1.520276494303527</v>
+        <v>-2.823035753826446</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.560776902192234</v>
       </c>
       <c r="E49">
-        <v>-14.69838262810981</v>
+        <v>-11.67237931212635</v>
       </c>
       <c r="F49">
-        <v>-3.477120365807795</v>
+        <v>-4.660953475027013</v>
       </c>
       <c r="G49">
-        <v>-2.019993411819895</v>
+        <v>-2.350677184646615</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.199958356589078</v>
       </c>
       <c r="E50">
-        <v>-13.50304210057113</v>
+        <v>-12.69636691168878</v>
       </c>
       <c r="F50">
-        <v>-3.855927808903592</v>
+        <v>-4.594301377062959</v>
       </c>
       <c r="G50">
-        <v>-1.848325072880987</v>
+        <v>-2.705541182092172</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.974393599381846</v>
       </c>
       <c r="E51">
-        <v>-15.2294277180413</v>
+        <v>-11.31372417071885</v>
       </c>
       <c r="F51">
-        <v>-3.427871438609156</v>
+        <v>-5.15157477852009</v>
       </c>
       <c r="G51">
-        <v>-1.694894529317925</v>
+        <v>-2.112672134191792</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.903297506983289</v>
       </c>
       <c r="E52">
-        <v>-15.317809945249</v>
+        <v>-11.91295902225784</v>
       </c>
       <c r="F52">
-        <v>-3.988985979713068</v>
+        <v>-4.930454525853804</v>
       </c>
       <c r="G52">
-        <v>-2.069039143984198</v>
+        <v>-2.260448265973779</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.991257626681631</v>
       </c>
       <c r="E53">
-        <v>-14.04104745505241</v>
+        <v>-11.22424152432729</v>
       </c>
       <c r="F53">
-        <v>-4.263814261307263</v>
+        <v>-5.011481283358638</v>
       </c>
       <c r="G53">
-        <v>-2.09582807848798</v>
+        <v>-1.960890242307286</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.230319177009446</v>
       </c>
       <c r="E54">
-        <v>-13.92344751354722</v>
+        <v>-10.48728672126703</v>
       </c>
       <c r="F54">
-        <v>-3.782475642929957</v>
+        <v>-4.918923651606836</v>
       </c>
       <c r="G54">
-        <v>-2.574291293642227</v>
+        <v>-2.568527633858356</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.601519951924848</v>
       </c>
       <c r="E55">
-        <v>-14.54283860289435</v>
+        <v>-9.639026555572242</v>
       </c>
       <c r="F55">
-        <v>-3.955073446609859</v>
+        <v>-5.031825986771394</v>
       </c>
       <c r="G55">
-        <v>-2.63278201223007</v>
+        <v>-2.807181551238876</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.074957813862341</v>
       </c>
       <c r="E56">
-        <v>-12.11447158712517</v>
+        <v>-9.907691861499309</v>
       </c>
       <c r="F56">
-        <v>-4.021661760283897</v>
+        <v>-5.212796928158793</v>
       </c>
       <c r="G56">
-        <v>-2.07266088080416</v>
+        <v>-2.952064266219541</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.612040967335679</v>
       </c>
       <c r="E57">
-        <v>-14.97896687762507</v>
+        <v>-9.040629471724673</v>
       </c>
       <c r="F57">
-        <v>-4.370084687045009</v>
+        <v>-5.3512494274953</v>
       </c>
       <c r="G57">
-        <v>-2.995948857888119</v>
+        <v>-2.767014702210899</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.16897816092823</v>
       </c>
       <c r="E58">
-        <v>-13.52869137735058</v>
+        <v>-9.788502425617425</v>
       </c>
       <c r="F58">
-        <v>-3.880317430344218</v>
+        <v>-5.190103803159101</v>
       </c>
       <c r="G58">
-        <v>-2.411938829850829</v>
+        <v>-3.232666106128166</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.705428915341882</v>
       </c>
       <c r="E59">
-        <v>-12.38756574063173</v>
+        <v>-10.4683169436489</v>
       </c>
       <c r="F59">
-        <v>-4.006474472320972</v>
+        <v>-5.238108522518735</v>
       </c>
       <c r="G59">
-        <v>-3.475160256334242</v>
+        <v>-2.656972168485525</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.191453069221118</v>
       </c>
       <c r="E60">
-        <v>-12.75713903287172</v>
+        <v>-9.545586022897972</v>
       </c>
       <c r="F60">
-        <v>-3.948197997166623</v>
+        <v>-5.305251842352649</v>
       </c>
       <c r="G60">
-        <v>-1.732581779736988</v>
+        <v>-3.041478790689716</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.614485401573994</v>
       </c>
       <c r="E61">
-        <v>-12.37711402262203</v>
+        <v>-8.83427596814315</v>
       </c>
       <c r="F61">
-        <v>-4.354791368054524</v>
+        <v>-5.386322503329831</v>
       </c>
       <c r="G61">
-        <v>-2.806774354137546</v>
+        <v>-3.130999252617148</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.970611120291851</v>
       </c>
       <c r="E62">
-        <v>-12.26953559409581</v>
+        <v>-9.770252675366514</v>
       </c>
       <c r="F62">
-        <v>-4.143493067683232</v>
+        <v>-5.163769175056702</v>
       </c>
       <c r="G62">
-        <v>-2.922746074923755</v>
+        <v>-3.159820862082043</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.258151851024639</v>
       </c>
       <c r="E63">
-        <v>-12.10322738616412</v>
+        <v>-8.48558799802654</v>
       </c>
       <c r="F63">
-        <v>-4.159714986532255</v>
+        <v>-5.101388967788886</v>
       </c>
       <c r="G63">
-        <v>-3.136557658577584</v>
+        <v>-2.763896168312905</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.478420902119964</v>
       </c>
       <c r="E64">
-        <v>-12.0101717737805</v>
+        <v>-8.241906283199791</v>
       </c>
       <c r="F64">
-        <v>-4.230647258866574</v>
+        <v>-5.353365906209453</v>
       </c>
       <c r="G64">
-        <v>-2.479414369032254</v>
+        <v>-3.284966104557573</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.637369383234835</v>
       </c>
       <c r="E65">
-        <v>-11.44471933833874</v>
+        <v>-10.06274228304793</v>
       </c>
       <c r="F65">
-        <v>-4.205167505923864</v>
+        <v>-5.424984895120692</v>
       </c>
       <c r="G65">
-        <v>-3.121650272014246</v>
+        <v>-3.341698923464063</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.744554136063194</v>
       </c>
       <c r="E66">
-        <v>-11.82051022539125</v>
+        <v>-9.34449913458737</v>
       </c>
       <c r="F66">
-        <v>-4.37452639305882</v>
+        <v>-4.997965640814561</v>
       </c>
       <c r="G66">
-        <v>-3.447215941437253</v>
+        <v>-3.039694406644049</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.80969539947729</v>
       </c>
       <c r="E67">
-        <v>-11.3416739122942</v>
+        <v>-8.77537863519939</v>
       </c>
       <c r="F67">
-        <v>-3.972284436137825</v>
+        <v>-5.277561176811867</v>
       </c>
       <c r="G67">
-        <v>-3.319849322904873</v>
+        <v>-2.740146314614174</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.847639105075721</v>
       </c>
       <c r="E68">
-        <v>-11.51815307284712</v>
+        <v>-9.005311902938852</v>
       </c>
       <c r="F68">
-        <v>-4.200492200302463</v>
+        <v>-5.29412024119383</v>
       </c>
       <c r="G68">
-        <v>-2.768845433894116</v>
+        <v>-2.905769597398372</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.870977002423897</v>
       </c>
       <c r="E69">
-        <v>-12.19214850177874</v>
+        <v>-8.368314106649901</v>
       </c>
       <c r="F69">
-        <v>-4.580850347176301</v>
+        <v>-5.458764889439453</v>
       </c>
       <c r="G69">
-        <v>-3.127579459075081</v>
+        <v>-2.907679782174532</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.890172691961556</v>
       </c>
       <c r="E70">
-        <v>-12.02479421635127</v>
+        <v>-8.713388354508389</v>
       </c>
       <c r="F70">
-        <v>-4.162493330801245</v>
+        <v>-5.300218682013239</v>
       </c>
       <c r="G70">
-        <v>-2.562386571883008</v>
+        <v>-2.83800604075503</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.912348074859453</v>
       </c>
       <c r="E71">
-        <v>-11.53437406674259</v>
+        <v>-9.585943783254329</v>
       </c>
       <c r="F71">
-        <v>-4.135129042017166</v>
+        <v>-5.618066567937021</v>
       </c>
       <c r="G71">
-        <v>-2.63346398461116</v>
+        <v>-2.690988023901536</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.940220558296497</v>
       </c>
       <c r="E72">
-        <v>-11.33176108269141</v>
+        <v>-8.521444455219275</v>
       </c>
       <c r="F72">
-        <v>-3.954607904129486</v>
+        <v>-5.721666337168141</v>
       </c>
       <c r="G72">
-        <v>-3.224571822284648</v>
+        <v>-2.943099308899194</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.970042904832672</v>
       </c>
       <c r="E73">
-        <v>-12.35423164346127</v>
+        <v>-9.093476763394186</v>
       </c>
       <c r="F73">
-        <v>-4.341159754074056</v>
+        <v>-5.643763353139264</v>
       </c>
       <c r="G73">
-        <v>-3.021976366917869</v>
+        <v>-2.820718371948956</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.994375492797866</v>
       </c>
       <c r="E74">
-        <v>-13.30527911218216</v>
+        <v>-9.053676005340771</v>
       </c>
       <c r="F74">
-        <v>-4.718421463596229</v>
+        <v>-5.677816708700949</v>
       </c>
       <c r="G74">
-        <v>-3.097407147030163</v>
+        <v>-2.409313567238186</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.011930959480308</v>
       </c>
       <c r="E75">
-        <v>-11.74624778013947</v>
+        <v>-9.695351715279646</v>
       </c>
       <c r="F75">
-        <v>-4.208321928993724</v>
+        <v>-5.758370468418784</v>
       </c>
       <c r="G75">
-        <v>-2.181279879947648</v>
+        <v>-2.285075414240417</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.024414158889405</v>
       </c>
       <c r="E76">
-        <v>-12.55254257720517</v>
+        <v>-10.34898259659877</v>
       </c>
       <c r="F76">
-        <v>-4.638300940030058</v>
+        <v>-5.725859532961112</v>
       </c>
       <c r="G76">
-        <v>-2.70600465846767</v>
+        <v>-1.897619095960736</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.036053063259377</v>
       </c>
       <c r="E77">
-        <v>-12.80808889393202</v>
+        <v>-10.57816866612697</v>
       </c>
       <c r="F77">
-        <v>-4.474762162267171</v>
+        <v>-6.05126958490505</v>
       </c>
       <c r="G77">
-        <v>-2.358516556483609</v>
+        <v>-2.119005207808418</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.051654618576038</v>
       </c>
       <c r="E78">
-        <v>-12.86863911988858</v>
+        <v>-10.87666755881657</v>
       </c>
       <c r="F78">
-        <v>-4.78159607520333</v>
+        <v>-5.814117109524982</v>
       </c>
       <c r="G78">
-        <v>-3.235506554200861</v>
+        <v>-2.457372756831786</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.072043068186584</v>
       </c>
       <c r="E79">
-        <v>-13.39079934381702</v>
+        <v>-11.52419405717335</v>
       </c>
       <c r="F79">
-        <v>-5.177328721073127</v>
+        <v>-6.265105174631118</v>
       </c>
       <c r="G79">
-        <v>-2.093090257327002</v>
+        <v>-2.339835148005502</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.090637064734594</v>
       </c>
       <c r="E80">
-        <v>-14.2696357660116</v>
+        <v>-12.33495392961062</v>
       </c>
       <c r="F80">
-        <v>-4.963434317261461</v>
+        <v>-6.218746421300846</v>
       </c>
       <c r="G80">
-        <v>-2.395064979237163</v>
+        <v>-2.344863866679655</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.099873337830219</v>
       </c>
       <c r="E81">
-        <v>-14.68669916517002</v>
+        <v>-12.68527215036999</v>
       </c>
       <c r="F81">
-        <v>-4.421288561314254</v>
+        <v>-5.982404917608119</v>
       </c>
       <c r="G81">
-        <v>-2.660411825300828</v>
+        <v>-2.220278106400262</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.09168934695664</v>
       </c>
       <c r="E82">
-        <v>-16.68441735975777</v>
+        <v>-13.53934234821662</v>
       </c>
       <c r="F82">
-        <v>-4.79965448458436</v>
+        <v>-6.28888428929588</v>
       </c>
       <c r="G82">
-        <v>-2.791982836668082</v>
+        <v>-2.248616376216424</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.055261493026826</v>
       </c>
       <c r="E83">
-        <v>-15.78791536045927</v>
+        <v>-14.28275022673781</v>
       </c>
       <c r="F83">
-        <v>-5.160982547113685</v>
+        <v>-6.321766333350006</v>
       </c>
       <c r="G83">
-        <v>-2.344277900119204</v>
+        <v>-1.738755947167729</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.978655343561986</v>
       </c>
       <c r="E84">
-        <v>-16.38398028019289</v>
+        <v>-14.98167943355566</v>
       </c>
       <c r="F84">
-        <v>-5.458635664124617</v>
+        <v>-6.378803570869766</v>
       </c>
       <c r="G84">
-        <v>-3.272051666408875</v>
+        <v>-1.471594922148544</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.84985644501513</v>
       </c>
       <c r="E85">
-        <v>-18.87904266114704</v>
+        <v>-16.93601031867592</v>
       </c>
       <c r="F85">
-        <v>-5.064192786300979</v>
+        <v>-6.522480169232028</v>
       </c>
       <c r="G85">
-        <v>-2.620456851187364</v>
+        <v>-1.78649401384402</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.658011069823317</v>
       </c>
       <c r="E86">
-        <v>-19.10084731804273</v>
+        <v>-17.07477181921895</v>
       </c>
       <c r="F86">
-        <v>-5.170519541022115</v>
+        <v>-6.255976151668565</v>
       </c>
       <c r="G86">
-        <v>-2.684843651380649</v>
+        <v>-1.942553130565263</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.393920380285675</v>
       </c>
       <c r="E87">
-        <v>-20.18751805481934</v>
+        <v>-18.98141787303844</v>
       </c>
       <c r="F87">
-        <v>-5.13793985107001</v>
+        <v>-6.311698355936382</v>
       </c>
       <c r="G87">
-        <v>-2.84105174265116</v>
+        <v>-1.777184759787589</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.058822720300734</v>
       </c>
       <c r="E88">
-        <v>-22.22221123967972</v>
+        <v>-19.27028922998774</v>
       </c>
       <c r="F88">
-        <v>-4.979902261229115</v>
+        <v>-6.571629692342331</v>
       </c>
       <c r="G88">
-        <v>-1.915350377869072</v>
+        <v>-1.495146143114919</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.661850289357774</v>
       </c>
       <c r="E89">
-        <v>-23.9337887471448</v>
+        <v>-21.23756249382192</v>
       </c>
       <c r="F89">
-        <v>-5.623797213629588</v>
+        <v>-6.392279451778509</v>
       </c>
       <c r="G89">
-        <v>-2.509841593083695</v>
+        <v>-1.802149583699233</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.222807407191038</v>
       </c>
       <c r="E90">
-        <v>-24.72359537034858</v>
+        <v>-22.78381900068897</v>
       </c>
       <c r="F90">
-        <v>-5.492391635788697</v>
+        <v>-6.715476106022167</v>
       </c>
       <c r="G90">
-        <v>-2.384398401509631</v>
+        <v>-2.115578793175272</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.773105210067604</v>
       </c>
       <c r="E91">
-        <v>-26.93783802113908</v>
+        <v>-24.55986386412725</v>
       </c>
       <c r="F91">
-        <v>-5.273826896560047</v>
+        <v>-6.257244382162251</v>
       </c>
       <c r="G91">
-        <v>-2.40261964415778</v>
+        <v>-2.39203914061427</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.35203720313494</v>
       </c>
       <c r="E92">
-        <v>-28.75453952421822</v>
+        <v>-27.30421421072965</v>
       </c>
       <c r="F92">
-        <v>-5.634739947020569</v>
+        <v>-6.657011591467383</v>
       </c>
       <c r="G92">
-        <v>-3.374797757765696</v>
+        <v>-2.722775882169618</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.999626421731023</v>
       </c>
       <c r="E93">
-        <v>-30.78937309177283</v>
+        <v>-29.25961834418972</v>
       </c>
       <c r="F93">
-        <v>-5.631651793342932</v>
+        <v>-6.250281125774319</v>
       </c>
       <c r="G93">
-        <v>-3.13276046284404</v>
+        <v>-2.742410727763036</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.751395261122823</v>
       </c>
       <c r="E94">
-        <v>-31.44131485228709</v>
+        <v>-31.03345331231225</v>
       </c>
       <c r="F94">
-        <v>-5.090966449126862</v>
+        <v>-6.143379898259341</v>
       </c>
       <c r="G94">
-        <v>-2.999511004888375</v>
+        <v>-3.429554180985241</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.637855328915223</v>
       </c>
       <c r="E95">
-        <v>-34.47043375838783</v>
+        <v>-33.44538649590761</v>
       </c>
       <c r="F95">
-        <v>-4.918835844662138</v>
+        <v>-6.137613632768454</v>
       </c>
       <c r="G95">
-        <v>-4.773546285199783</v>
+        <v>-3.294195905521061</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.685895558295792</v>
       </c>
       <c r="E96">
-        <v>-37.55299545049009</v>
+        <v>-34.75766580774635</v>
       </c>
       <c r="F96">
-        <v>-5.445196231381598</v>
+        <v>-6.179116496383514</v>
       </c>
       <c r="G96">
-        <v>-4.155629649749277</v>
+        <v>-3.728837429371975</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.894195537229334</v>
       </c>
       <c r="E97">
-        <v>-38.41491122955502</v>
+        <v>-36.41748285730376</v>
       </c>
       <c r="F97">
-        <v>-5.0124463313829</v>
+        <v>-6.062533724848318</v>
       </c>
       <c r="G97">
-        <v>-4.305782753228461</v>
+        <v>-4.416934319709491</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.277477086448171</v>
       </c>
       <c r="E98">
-        <v>-42.01396576036512</v>
+        <v>-39.73622258280206</v>
       </c>
       <c r="F98">
-        <v>-5.039110649711612</v>
+        <v>-6.007179729891047</v>
       </c>
       <c r="G98">
-        <v>-5.014693043371375</v>
+        <v>-4.5995870487477</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.790622091862242</v>
       </c>
       <c r="E99">
-        <v>-45.12509985921877</v>
+        <v>-42.71131000128028</v>
       </c>
       <c r="F99">
-        <v>-5.438665382777926</v>
+        <v>-6.041543723228782</v>
       </c>
       <c r="G99">
-        <v>-4.624359861018067</v>
+        <v>-5.075550802019797</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.450519297767766</v>
       </c>
       <c r="E100">
-        <v>-46.59378134209744</v>
+        <v>-44.84132529976512</v>
       </c>
       <c r="F100">
-        <v>-5.149456643071132</v>
+        <v>-5.773175050641617</v>
       </c>
       <c r="G100">
-        <v>-5.553868353170317</v>
+        <v>-5.816378061706825</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.148714145972976</v>
       </c>
       <c r="E101">
-        <v>-48.92164793421439</v>
+        <v>-47.16538118100461</v>
       </c>
       <c r="F101">
-        <v>-4.849103048327073</v>
+        <v>-5.4321477880527</v>
       </c>
       <c r="G101">
-        <v>-5.779717080404936</v>
+        <v>-5.684164804504952</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.971342735221363</v>
       </c>
       <c r="E102">
-        <v>-50.5889664009655</v>
+        <v>-49.0984169171038</v>
       </c>
       <c r="F102">
-        <v>-4.850087977169002</v>
+        <v>-5.2990531690775</v>
       </c>
       <c r="G102">
-        <v>-6.182593919806543</v>
+        <v>-6.510907342027145</v>
       </c>
     </row>
   </sheetData>
